--- a/AAII_Financials/Quarterly/BEPC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEPC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>BEPC</t>
   </si>
@@ -656,138 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
@@ -797,98 +798,101 @@
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1076000</v>
+      </c>
+      <c r="E8" s="3">
         <v>883000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>938000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>931000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>952000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>907000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>987000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1041000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>965000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1149000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>919000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1029000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>940000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1079000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>956000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>896000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>997000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>929000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>905000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>806000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>817000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>839000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>746000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>724000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>764000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>853000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>781000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>736000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1709000</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
@@ -898,98 +902,101 @@
       <c r="AI8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>453000</v>
+      </c>
+      <c r="E9" s="3">
         <v>415000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>404000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>370000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>353000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>368000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>457000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>407000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>419000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>484000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>466000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>388000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>308000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>304000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>294000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>293000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>296000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>291000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>344000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>254000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>249000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>338000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>280000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>238000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>264000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>279000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>268000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>259000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>526000</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,98 +1006,101 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>623000</v>
+      </c>
+      <c r="E10" s="3">
         <v>468000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>534000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>561000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>599000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>539000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>530000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>634000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>546000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>665000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>453000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>641000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>632000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>775000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>662000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>603000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>701000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>638000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>561000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>552000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>568000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>501000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>466000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>486000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>500000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>574000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>513000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>477000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1183000</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1100,8 +1110,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1137,8 +1150,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1238,8 +1252,11 @@
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,83 +1356,86 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>704000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2035000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>591000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>125000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1276000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-223000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1251000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>612000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>277000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-548000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>401000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1393000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-380000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1063000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1026000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-603000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-1080000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>909000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-193000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-286000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-694000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-94000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1398000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1163000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1440,98 +1460,101 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E15" s="3">
         <v>294000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>301000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>313000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>319000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>307000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>292000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>313000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>312000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>345000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>389000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>320000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>327000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>306000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>309000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>288000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>286000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>296000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>281000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>269000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>275000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>290000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>259000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>293000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>254000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>259000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>273000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>247000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>463000</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1541,8 +1564,11 @@
       <c r="AI15" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,98 +1601,99 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>799000</v>
+      </c>
+      <c r="E17" s="3">
         <v>755000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>740000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>709000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>698000</v>
       </c>
       <c r="H17" s="3">
         <v>698000</v>
       </c>
       <c r="I17" s="3">
+        <v>698000</v>
+      </c>
+      <c r="J17" s="3">
         <v>784000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>748000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>753000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>850000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>849000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>734000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>667000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>646000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-368000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-461000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1510000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>504000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>297000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-97000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>721000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2342000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1809000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>516000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>566000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>682000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>528000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1053000</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,98 +1703,101 @@
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E18" s="3">
         <v>128000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>198000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>222000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>254000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>209000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>203000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>293000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>212000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>299000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>70000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>295000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>273000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>433000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1324000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>862000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1458000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-581000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>401000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>509000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>914000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>118000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1596000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1085000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>248000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>287000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>99000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>208000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>656000</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,8 +1807,11 @@
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,98 +1847,99 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E20" s="3">
         <v>43000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-16000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-67000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-126000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-73000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-40000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-36000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-40000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>34000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-66000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-35000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-82000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>40000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-19000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>36000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>62000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>13000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>36000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>30000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1915,98 +1949,101 @@
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>644000</v>
+      </c>
+      <c r="E21" s="3">
         <v>379000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>515000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>602000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>572000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>499000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>621000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>616000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>597000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>684000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>495000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>632000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>640000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>818000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1667000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1084000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1748000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-320000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>600000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>818000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1170000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>444000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1275000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-779000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>461000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>582000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>402000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>653000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>908000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2016,98 +2053,101 @@
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E22" s="3">
         <v>373000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>436000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>398000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>425000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>413000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>635000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>328000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>341000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>363000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>329000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>308000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>315000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>306000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>285000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>264000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>255000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>228000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>229000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>231000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>220000</v>
       </c>
       <c r="X22" s="3">
         <v>220000</v>
       </c>
       <c r="Y22" s="3">
+        <v>220000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>229000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>230000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>189000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>168000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>185000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>164000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>352000</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2117,98 +2157,101 @@
       <c r="AI22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-748000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2323000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-676000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-234000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1448000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1046000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-637000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-333000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>524000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-537000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1397000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>378000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-857000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1073000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>532000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1207000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-844000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>90000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>318000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>675000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1763000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1302000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>18000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>155000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>34000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>301000</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,98 +2261,101 @@
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-21000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-10000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>101000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>33000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-35000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>27000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>63000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>70000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>38000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-90000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>165000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>16000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-131000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>60000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-14000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>78000</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2365,11 @@
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,98 +2469,101 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-785000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2302000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-666000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-225000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1447000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>945000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-664000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-339000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>491000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-502000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1370000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>360000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-920000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1078000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>517000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1137000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-882000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>180000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>153000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>659000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-62000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1632000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1297000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>95000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-42000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>31000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>223000</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2521,98 +2573,101 @@
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-790000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2186000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-706000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-233000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1410000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>761000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-674000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-342000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>491000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-747000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1340000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>291000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1065000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>953000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>480000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1046000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-976000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>130000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>214000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>611000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1516000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1295000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>13000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>62000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>37000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>125000</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2677,11 @@
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2824,8 +2885,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,98 +3093,101 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-43000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>16000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>67000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>126000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>73000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>40000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>36000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>40000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>79000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-34000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>66000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>35000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>82000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-40000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>19000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-62000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>41000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>10000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3000</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,98 +3197,101 @@
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-790000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2186000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-706000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-233000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1410000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>761000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-674000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-342000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>491000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-747000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1340000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>291000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1065000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>953000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>480000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1046000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-976000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>130000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>214000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>611000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1516000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1295000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>13000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>62000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>37000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>125000</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3301,11 @@
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,98 +3405,101 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-790000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2186000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-706000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-233000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1410000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>761000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-674000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-342000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>491000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-747000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1340000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>291000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1065000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>953000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>480000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1046000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-976000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>130000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>214000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>611000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1516000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1295000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>13000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>62000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>37000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>125000</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3430,103 +3509,106 @@
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3618,11 @@
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,89 +3696,90 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>756000</v>
+      </c>
+      <c r="E41" s="3">
         <v>651000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>682000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>559000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>556000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>614000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>624000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>619000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>614000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>639000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>627000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>513000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>595000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>657000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>642000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>566000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>571000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>558000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>410000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>413000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>396000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>298000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>355000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>377000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>147000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>152000</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,71 +3798,74 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E42" s="3">
         <v>54000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>60000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>88000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>93000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>88000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>129000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>111000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>117000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>603000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>825000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>733000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>539000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>434000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>326000</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3791,8 +3881,8 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3812,89 +3902,92 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3313000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2709000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2319000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3521000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2686000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1794000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1968000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1977000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1749000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1671000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2070000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1614000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1628000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1644000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1262000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>886000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>916000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>957000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1157000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1239000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1224000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>986000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>968000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>799000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>428000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>422000</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3913,70 +4006,73 @@
       <c r="AI43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E44" s="3">
         <v>33000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>51000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>49000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>38000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>35000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>30000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>27000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>65000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>23000</v>
       </c>
       <c r="O44" s="3">
         <v>23000</v>
       </c>
       <c r="P44" s="3">
+        <v>23000</v>
+      </c>
+      <c r="Q44" s="3">
         <v>21000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>18000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>20000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>21000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>22000</v>
-      </c>
-      <c r="U44" s="3">
-        <v>20000</v>
       </c>
       <c r="V44" s="3">
         <v>20000</v>
       </c>
       <c r="W44" s="3">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="X44" s="3">
         <v>22000</v>
@@ -3984,8 +4080,8 @@
       <c r="Y44" s="3">
         <v>22000</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
+      <c r="Z44" s="3">
+        <v>22000</v>
       </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
@@ -4002,8 +4098,8 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF44" s="3">
-        <v>0</v>
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG44" s="3">
         <v>0</v>
@@ -4014,89 +4110,92 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2963000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2420000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>773000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1621000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>235000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>259000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>310000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1673000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>472000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>208000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>293000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>286000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>560000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>397000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>901000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>425000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>401000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>408000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>287000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>367000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1160000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1059000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>239000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>378000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>306000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>316000</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4115,89 +4214,92 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7221000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5975000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3943000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5919000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3703000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2803000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3114000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4446000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2948000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2769000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3298000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2716000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3053000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2815000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3426000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2722000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2642000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2484000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2308000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2365000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2802000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2365000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1584000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1554000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>881000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>890000</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,89 +4318,92 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>999000</v>
+      </c>
+      <c r="E47" s="3">
         <v>948000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1014000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>966000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>816000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>774000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>753000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>631000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>637000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>911000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>644000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>554000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>917000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>561000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>451000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>505000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>454000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>460000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>455000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>372000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>374000</v>
-      </c>
-      <c r="X47" s="3">
-        <v>372000</v>
       </c>
       <c r="Y47" s="3">
         <v>372000</v>
       </c>
       <c r="Z47" s="3">
+        <v>372000</v>
+      </c>
+      <c r="AA47" s="3">
         <v>345000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>338000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>339000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4317,89 +4422,92 @@
       <c r="AI47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38771000</v>
+      </c>
+      <c r="E48" s="3">
         <v>38456000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39699000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38924000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40094000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39731000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38696000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36678000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37760000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>39485000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44038000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39205000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>39241000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38264000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>37828000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36158000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>37258000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>38654000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>37915000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>33660000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>34248000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>34009000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>36097000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>31170000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20699000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20157000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4418,89 +4526,92 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>847000</v>
+      </c>
+      <c r="E49" s="3">
         <v>825000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>809000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>783000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>755000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>727000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>692000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>734000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>794000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>847000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>861000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>814000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>797000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>953000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>931000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>956000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1029000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1107000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1067000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1099000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1121000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1126000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1203000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1106000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>715000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>662000</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4519,8 +4630,11 @@
       <c r="AI49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,89 +4838,92 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>636000</v>
+      </c>
+      <c r="E52" s="3">
         <v>605000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>623000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>578000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>579000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>867000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>818000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>270000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>384000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>147000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>469000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>456000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>127000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>579000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>652000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>464000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>386000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>368000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>241000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>266000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>260000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>261000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>217000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>168000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>37000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>49000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4942,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,89 +5046,92 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48671000</v>
+      </c>
+      <c r="E54" s="3">
         <v>46994000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>46267000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47315000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46034000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44964000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44129000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42875000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42613000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44240000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>49421000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43801000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>44206000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>43250000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>43288000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40805000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>41769000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43073000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41986000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>37762000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>38805000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>38133000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39473000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34343000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22670000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22097000</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5024,8 +5150,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,89 +5228,90 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1594000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1315000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1349000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1831000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1569000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>658000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>716000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>725000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>749000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>650000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>640000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>470000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>652000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>702000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>154000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>132000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>108000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>103000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>118000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>126000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>235000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>100000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>114000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>118000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>52000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>47000</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5199,89 +5330,92 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1313000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2355000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2801000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1926000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1592000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1358000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1307000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1191000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1360000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1424000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1922000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1052000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1025000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1501000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1325000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1385000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1398000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1830000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1477000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1124000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>956000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>926000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>916000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1416000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>685000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>155000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5300,89 +5434,92 @@
       <c r="AI58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14987000</v>
+      </c>
+      <c r="E59" s="3">
         <v>13997000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11002000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11082000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10213000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8861000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8924000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6445000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4901000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4617000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5256000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4199000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5868000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5778000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5772000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6839000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7189000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8398000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7380000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7805000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8637000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9437000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8920000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7022000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>453000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>415000</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5401,89 +5538,92 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18155000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17938000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15453000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15104000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13714000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11237000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11254000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8691000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7335000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7112000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8335000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6085000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7857000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8284000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7251000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8356000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8695000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10331000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8975000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9055000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9828000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10463000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9950000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8556000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1190000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>617000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5502,89 +5642,92 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14136000</v>
+      </c>
+      <c r="E61" s="3">
         <v>12669000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12763000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12771000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12797000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12780000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12786000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12606000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12840000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13095000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14651000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12743000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12771000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12450000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12754000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12229000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12581000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11940000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12060000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11954000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11981000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11401000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12298000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11173000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5036000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5196000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5603,89 +5746,92 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2110000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1994000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1428000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1898000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1929000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1816000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1442000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1953000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2052000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2226000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3430000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1475000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1441000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1397000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6459000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6492000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6665000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6922000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6726000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5847000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5552000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5531000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5500000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4898000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3122000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3009000</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5704,8 +5850,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,89 +6162,92 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41925000</v>
+      </c>
+      <c r="E66" s="3">
         <v>40011000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37035000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36780000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35280000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32522000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32021000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28689000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27774000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28224000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32292000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26043000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27712000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>27539000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37415000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>36627000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37957000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40059000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>38319000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>36211000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>37246000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>37319000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>38296000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33048000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15680000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15024000</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6108,8 +6266,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,8 +6720,11 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6593,8 +6767,8 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -6650,8 +6824,11 @@
       <c r="AI72" s="3">
         <v>0</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,89 +7136,92 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3323000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2632000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-406000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-212000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>116000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1436000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1341000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4876000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5760000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6095000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5787000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6676000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5384000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4920000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5873000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4178000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3812000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3014000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3667000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1551000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1559000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>814000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1177000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1295000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6990000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7073000</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7054,8 +7240,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,103 +7344,106 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7261,98 +7453,101 @@
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-790000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2186000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-706000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-233000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1410000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>761000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-674000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-342000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>491000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-747000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1340000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>291000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1065000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>953000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>480000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1046000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-976000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>130000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>214000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>611000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1516000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1295000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>13000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>62000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>37000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>125000</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7362,8 +7557,11 @@
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,98 +7597,99 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>319000</v>
+      </c>
+      <c r="E83" s="3">
         <v>307000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>292000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>313000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>312000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>345000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>389000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>320000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>327000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>306000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>309000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>288000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>286000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>296000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>309000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>288000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>286000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>296000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>281000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>269000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>275000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>290000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>259000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>293000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>254000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>259000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>273000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>455000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>255000</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7500,8 +7699,11 @@
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,98 +8219,101 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E89" s="3">
         <v>57000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>259000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>139000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>110000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-156000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>308000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>140000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>257000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>471000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>288000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>253000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>592000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>411000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>290000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>323000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>252000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>230000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-116000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>287000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>121000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>141000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>363000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>367000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>209000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>505000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>642000</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8106,8 +8323,11 @@
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,98 +8363,99 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-277000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-195000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-348000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-240000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-302000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-248000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-303000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-162000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-207000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-277000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-523000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-185000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-158000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-162000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-223000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-210000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-246000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-168000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-791000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-158000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-166000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-239000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-175000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-125000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-52000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8244,8 +8465,11 @@
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,98 +8673,101 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-306000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-251000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>56000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-344000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-252000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-125000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-118000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-51000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-371000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-643000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-53000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-95000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-227000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-29000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-258000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-260000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-191000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-707000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>212000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-212000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-277000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-43000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-319000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>749000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-825000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-62000</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8547,8 +8777,11 @@
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,26 +8817,27 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3">
         <v>5000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>3</v>
       </c>
@@ -8628,8 +8862,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8685,8 +8919,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,98 +9231,101 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E100" s="3">
         <v>177000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>62000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>109000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-179000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>104000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>303000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-166000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-82000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>137000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>267000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-310000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-231000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-362000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-440000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-32000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>86000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>493000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-180000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>422000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-115000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-206000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-81000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>226000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-433000</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9089,97 +9335,100 @@
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E101" s="3">
         <v>27000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-15000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-19000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-30000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>19000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>19000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-21000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-18000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>19000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-21000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-18000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-19000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-9000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>15000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF101" s="3" t="s">
-        <v>3</v>
+      <c r="AF101" s="3">
+        <v>0</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>3</v>
@@ -9190,98 +9439,101 @@
       <c r="AI101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>131000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-57000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>14000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>114000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-85000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-59000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-39000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>148000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>17000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>98000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>104000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>147000</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9289,6 +9541,9 @@
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
